--- a/artfynd/A 56314-2022 artfynd.xlsx
+++ b/artfynd/A 56314-2022 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117724946</v>
+        <v>117724945</v>
       </c>
       <c r="B3" t="n">
         <v>74578</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523832</v>
+        <v>523697</v>
       </c>
       <c r="R3" t="n">
-        <v>6388035</v>
+        <v>6387818</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117724945</v>
+        <v>117724946</v>
       </c>
       <c r="B4" t="n">
         <v>74578</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523697</v>
+        <v>523832</v>
       </c>
       <c r="R4" t="n">
-        <v>6387818</v>
+        <v>6388035</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 56314-2022 artfynd.xlsx
+++ b/artfynd/A 56314-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117724943</v>
       </c>
       <c r="B2" t="n">
-        <v>77820</v>
+        <v>77822</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117724945</v>
+        <v>117724946</v>
       </c>
       <c r="B3" t="n">
-        <v>74578</v>
+        <v>74580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523697</v>
+        <v>523832</v>
       </c>
       <c r="R3" t="n">
-        <v>6387818</v>
+        <v>6388035</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117724946</v>
+        <v>117724945</v>
       </c>
       <c r="B4" t="n">
-        <v>74578</v>
+        <v>74580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523832</v>
+        <v>523697</v>
       </c>
       <c r="R4" t="n">
-        <v>6388035</v>
+        <v>6387818</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 56314-2022 artfynd.xlsx
+++ b/artfynd/A 56314-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2624,6 +2624,231 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>126363690</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58513</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>larv</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Rockegölen, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>523715</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6387970</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Eksjö</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ingatorp</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Caroline Ryding</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Groddjursinventering Ingatorp</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>126363691</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58513</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>larv</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Rockegölen, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>523671</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6387932</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Eksjö</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ingatorp</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Groddjursinventering Ingatorp</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56314-2022 artfynd.xlsx
+++ b/artfynd/A 56314-2022 artfynd.xlsx
@@ -2629,7 +2629,7 @@
         <v>126363690</v>
       </c>
       <c r="B21" t="n">
-        <v>58513</v>
+        <v>58516</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>126363691</v>
       </c>
       <c r="B22" t="n">
-        <v>58513</v>
+        <v>58516</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
